--- a/results/meshconv/Rae2822-Gridconv.xlsx
+++ b/results/meshconv/Rae2822-Gridconv.xlsx
@@ -991,35 +991,35 @@
                     <a:lumOff val="25000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
-                <a:ea typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
-                <a:sym typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
+                <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+                <a:ea typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+                <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+                <a:sym typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
               <a:rPr lang="ru-RU" altLang="en-US" sz="1680">
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
-                <a:ea typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
-                <a:sym typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
+                <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+                <a:ea typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+                <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+                <a:sym typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
               </a:rPr>
-              <a:t>Ошибка </a:t>
+              <a:t>Сеточная сходимость на </a:t>
             </a:r>
             <a:r>
               <a:rPr altLang="ru-RU" sz="1680">
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
-                <a:ea typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
-                <a:sym typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
+                <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+                <a:ea typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+                <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+                <a:sym typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
               </a:rPr>
-              <a:t>Cxa</a:t>
+              <a:t>RAE2822 </a:t>
             </a:r>
             <a:endParaRPr altLang="ru-RU" sz="1680">
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
-              <a:ea typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
-              <a:sym typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+              <a:ea typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+              <a:sym typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
             </a:endParaRPr>
           </a:p>
         </c:rich>
@@ -1028,8 +1028,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.419150080688542"/>
-          <c:y val="0.0220048899755501"/>
+          <c:x val="0.222270037654653"/>
+          <c:y val="0.0268948655256723"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -1110,7 +1110,7 @@
                   <c:v>96</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>120</c:v>
+                  <c:v>121</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>145</c:v>
@@ -1123,112 +1123,33 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$H$2:$H$9</c:f>
+              <c:f>Sheet1!$G$2:$G$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>-0.060472440944882</c:v>
+                  <c:v>134.68</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.0350393700787401</c:v>
+                  <c:v>122.55</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.0462204724409448</c:v>
+                  <c:v>121.13</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.0403149606299213</c:v>
+                  <c:v>121.88</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.0407874015748031</c:v>
+                  <c:v>121.82</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.048267716535433</c:v>
+                  <c:v>121.84</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.0407874015748031</c:v>
+                  <c:v>121.82</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.0396850393700787</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>"Относительная ошибка Cxa Dens-based"</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Относительная ошибка Cxa Dens-based</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:dLbls>
-            <c:delete val="1"/>
-          </c:dLbls>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$E$10:$E$12</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>78</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>96</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>120</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$H$10:$H$12</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>0.0324409448818897</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.0338582677165354</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.0382677165354331</c:v>
+                  <c:v>121.96</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1250,6 +1171,7 @@
         <c:axId val="561000989"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="200"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -1266,6 +1188,44 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr defTabSz="914400">
+                  <a:defRPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+                    <a:ea typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+                    <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+                    <a:sym typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ru-RU" altLang="en-US"/>
+                  <a:t>Количество ячеек (тысячи)</a:t>
+                </a:r>
+                <a:endParaRPr lang="ru-RU" altLang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -1295,10 +1255,10 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
-                <a:ea typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
-                <a:sym typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
+                <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+                <a:ea typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+                <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+                <a:sym typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
@@ -1327,7 +1287,45 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr defTabSz="914400">
+                  <a:defRPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+                    <a:ea typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+                    <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+                    <a:sym typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr altLang="ru-RU"/>
+                  <a:t>Cxa (counts)</a:t>
+                </a:r>
+                <a:endParaRPr altLang="ru-RU"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1356,10 +1354,10 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
-                <a:ea typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
-                <a:sym typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
+                <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+                <a:ea typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+                <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+                <a:sym typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
@@ -1382,87 +1380,14 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:legendEntry>
-        <c:idx val="0"/>
-        <c:txPr>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
-                <a:ea typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
-                <a:sym typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
-        </c:txPr>
-      </c:legendEntry>
-      <c:legendEntry>
-        <c:idx val="1"/>
-        <c:txPr>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
-                <a:ea typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
-                <a:sym typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
-        </c:txPr>
-      </c:legendEntry>
-      <c:layout/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
-              <a:ea typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
-              <a:sym typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
-            </a:defRPr>
-          </a:pPr>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext uri="{0b15fc19-7d7d-44ad-8c2d-2c3a37ce22c3}">
+        <chartProps xmlns="https://web.wps.cn/et/2018/main" chartId="{57e7b9f8-eb41-4b62-a59d-3d858e62ad09}"/>
+      </c:ext>
+    </c:extLst>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1485,10 +1410,10 @@
     <a:p>
       <a:pPr>
         <a:defRPr lang="en-US" sz="1400">
-          <a:latin typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
-          <a:ea typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
-          <a:cs typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
-          <a:sym typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
+          <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+          <a:ea typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+          <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+          <a:sym typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
         </a:defRPr>
       </a:pPr>
     </a:p>
@@ -1626,7 +1551,7 @@
                   <c:v>96</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>120</c:v>
+                  <c:v>121</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>145</c:v>
@@ -1639,112 +1564,33 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$K$2:$K$9</c:f>
+              <c:f>Sheet1!$J$2:$J$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>-0.0143578947368421</c:v>
+                  <c:v>-0.096364</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.0177157894736843</c:v>
+                  <c:v>-0.093317</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.0237263157894737</c:v>
+                  <c:v>-0.092746</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.0296842105263158</c:v>
+                  <c:v>-0.09218</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.0319473684210526</c:v>
+                  <c:v>-0.091965</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.0378947368421053</c:v>
+                  <c:v>-0.0914</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.0319473684210526</c:v>
+                  <c:v>-0.091965</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.036421052631579</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>"Относительная ошибка mz Dens-based"</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Относительная ошибка mz Dens-based</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:dLbls>
-            <c:delete val="1"/>
-          </c:dLbls>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$E$10:$E$12</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>78</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>96</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>120</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$K$10:$K$12</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>0.0351157894736843</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.0356210526315789</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.0376842105263158</c:v>
+                  <c:v>-0.09154</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1843,7 +1689,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1902,29 +1748,6 @@
       <c:legendPos val="b"/>
       <c:legendEntry>
         <c:idx val="0"/>
-        <c:txPr>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
-                <a:ea typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
-                <a:sym typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
-        </c:txPr>
-      </c:legendEntry>
-      <c:legendEntry>
-        <c:idx val="1"/>
         <c:txPr>
           <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
@@ -3180,16 +3003,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>596900</xdr:colOff>
-      <xdr:row>1</xdr:row>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>53975</xdr:colOff>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>29845</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>403225</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>115570</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>84455</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>144145</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3197,8 +3020,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="11388725" y="220345"/>
-        <a:ext cx="5902325" cy="3895725"/>
+        <a:off x="13179425" y="791845"/>
+        <a:ext cx="6126480" cy="4114800"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3210,16 +3033,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>323850</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>933450</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>130175</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>530225</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3227,7 +3050,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="11725275" y="4314825"/>
+        <a:off x="8972550" y="6143625"/>
         <a:ext cx="5902325" cy="3895725"/>
       </xdr:xfrm>
       <a:graphic>
@@ -3499,18 +3322,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
     <col min="5" max="5" width="22.7142857142857" customWidth="1"/>
     <col min="6" max="6" width="9.57142857142857"/>
-    <col min="7" max="7" width="25.8571428571429" customWidth="1"/>
-    <col min="8" max="8" width="20.2857142857143" customWidth="1"/>
-    <col min="10" max="10" width="20.2857142857143" customWidth="1"/>
-    <col min="11" max="11" width="17.4285714285714" customWidth="1"/>
+    <col min="7" max="8" width="25.8571428571429" customWidth="1"/>
+    <col min="9" max="9" width="20.2857142857143" customWidth="1"/>
+    <col min="11" max="11" width="20.2857142857143" customWidth="1"/>
+    <col min="12" max="12" width="17.4285714285714" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3526,23 +3349,23 @@
       <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -3562,26 +3385,30 @@
         <v>0.013468</v>
       </c>
       <c r="G2">
+        <f>F2*10000</f>
+        <v>134.68</v>
+      </c>
+      <c r="H2">
         <f>($C$2-F2)*10000</f>
         <v>-7.68000000000001</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <f>($C$2-F2)/$C$2</f>
         <v>-0.060472440944882</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>-0.096364</v>
       </c>
-      <c r="J2">
-        <f>($C$3-I2)*10000</f>
+      <c r="K2">
+        <f>($C$3-J2)*10000</f>
         <v>13.64</v>
       </c>
-      <c r="K2">
-        <f>(C$3-I2)/$C$3</f>
+      <c r="L2">
+        <f>(C$3-J2)/$C$3</f>
         <v>-0.0143578947368421</v>
       </c>
     </row>
-    <row r="3" spans="2:11">
+    <row r="3" spans="2:12">
       <c r="B3" t="s">
         <v>11</v>
       </c>
@@ -3595,26 +3422,30 @@
         <v>0.012255</v>
       </c>
       <c r="G3">
-        <f t="shared" ref="G3:G11" si="0">ABS($C$2-F3)*10000</f>
+        <f t="shared" ref="G3:G9" si="0">F3*10000</f>
+        <v>122.55</v>
+      </c>
+      <c r="H3">
+        <f t="shared" ref="H3:H12" si="1">ABS($C$2-F3)*10000</f>
         <v>4.44999999999999</v>
       </c>
-      <c r="H3">
-        <f t="shared" ref="H3:H12" si="1">($C$2-F3)/$C$2</f>
+      <c r="I3">
+        <f t="shared" ref="I3:I12" si="2">($C$2-F3)/$C$2</f>
         <v>0.0350393700787401</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>-0.093317</v>
       </c>
-      <c r="J3">
-        <f t="shared" ref="J3:J10" si="2">($C$3-I3)*10000</f>
+      <c r="K3">
+        <f t="shared" ref="K3:K12" si="3">($C$3-J3)*10000</f>
         <v>-16.83</v>
       </c>
-      <c r="K3">
-        <f t="shared" ref="K3:K12" si="3">(C$3-I3)/$C$3</f>
+      <c r="L3">
+        <f t="shared" ref="L3:L12" si="4">(C$3-J3)/$C$3</f>
         <v>0.0177157894736843</v>
       </c>
     </row>
-    <row r="4" spans="5:11">
+    <row r="4" spans="5:12">
       <c r="E4">
         <v>53</v>
       </c>
@@ -3623,25 +3454,29 @@
       </c>
       <c r="G4">
         <f t="shared" si="0"/>
-        <v>5.86999999999999</v>
+        <v>121.13</v>
       </c>
       <c r="H4">
         <f t="shared" si="1"/>
+        <v>5.86999999999999</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="2"/>
         <v>0.0462204724409448</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>-0.092746</v>
-      </c>
-      <c r="J4">
-        <f t="shared" si="2"/>
-        <v>-22.5400000000001</v>
       </c>
       <c r="K4">
         <f t="shared" si="3"/>
+        <v>-22.5400000000001</v>
+      </c>
+      <c r="L4">
+        <f t="shared" si="4"/>
         <v>0.0237263157894737</v>
       </c>
     </row>
-    <row r="5" spans="5:11">
+    <row r="5" spans="5:12">
       <c r="E5">
         <v>78</v>
       </c>
@@ -3650,25 +3485,29 @@
       </c>
       <c r="G5">
         <f t="shared" si="0"/>
-        <v>5.12</v>
+        <v>121.88</v>
       </c>
       <c r="H5">
         <f t="shared" si="1"/>
+        <v>5.12</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="2"/>
         <v>0.0403149606299213</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>-0.09218</v>
-      </c>
-      <c r="J5">
-        <f t="shared" si="2"/>
-        <v>-28.2</v>
       </c>
       <c r="K5">
         <f t="shared" si="3"/>
+        <v>-28.2</v>
+      </c>
+      <c r="L5">
+        <f t="shared" si="4"/>
         <v>0.0296842105263158</v>
       </c>
     </row>
-    <row r="6" spans="5:11">
+    <row r="6" spans="5:12">
       <c r="E6">
         <v>96</v>
       </c>
@@ -3677,52 +3516,60 @@
       </c>
       <c r="G6">
         <f t="shared" si="0"/>
-        <v>5.17999999999999</v>
+        <v>121.82</v>
       </c>
       <c r="H6">
         <f t="shared" si="1"/>
+        <v>5.17999999999999</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="2"/>
         <v>0.0407874015748031</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>-0.091965</v>
-      </c>
-      <c r="J6">
-        <f t="shared" si="2"/>
-        <v>-30.35</v>
       </c>
       <c r="K6">
         <f t="shared" si="3"/>
+        <v>-30.35</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="4"/>
         <v>0.0319473684210526</v>
       </c>
     </row>
-    <row r="7" spans="5:11">
+    <row r="7" spans="5:12">
       <c r="E7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F7">
-        <v>0.012087</v>
+        <v>0.012184</v>
       </c>
       <c r="G7">
         <f t="shared" si="0"/>
-        <v>6.12999999999999</v>
+        <v>121.84</v>
       </c>
       <c r="H7">
         <f t="shared" si="1"/>
-        <v>0.048267716535433</v>
+        <v>5.15999999999999</v>
       </c>
       <c r="I7">
+        <f t="shared" si="2"/>
+        <v>0.0406299212598425</v>
+      </c>
+      <c r="J7">
         <v>-0.0914</v>
-      </c>
-      <c r="J7">
-        <f t="shared" si="2"/>
-        <v>-36.0000000000001</v>
       </c>
       <c r="K7">
         <f t="shared" si="3"/>
+        <v>-36.0000000000001</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="4"/>
         <v>0.0378947368421053</v>
       </c>
     </row>
-    <row r="8" spans="5:11">
+    <row r="8" spans="5:12">
       <c r="E8">
         <v>145</v>
       </c>
@@ -3730,26 +3577,30 @@
         <v>0.012182</v>
       </c>
       <c r="G8">
-        <f>ABS($C$2-F8)*10000</f>
-        <v>5.17999999999999</v>
+        <f t="shared" si="0"/>
+        <v>121.82</v>
       </c>
       <c r="H8">
         <f t="shared" si="1"/>
+        <v>5.17999999999999</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="2"/>
         <v>0.0407874015748031</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>-0.091965</v>
-      </c>
-      <c r="J8">
-        <f>($C$3-I8)*10000</f>
-        <v>-30.35</v>
       </c>
       <c r="K8">
         <f t="shared" si="3"/>
+        <v>-30.35</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="4"/>
         <v>0.0319473684210526</v>
       </c>
     </row>
-    <row r="9" spans="5:11">
+    <row r="9" spans="5:12">
       <c r="E9">
         <v>200</v>
       </c>
@@ -3757,26 +3608,30 @@
         <v>0.012196</v>
       </c>
       <c r="G9">
-        <f>ABS($C$2-F9)*10000</f>
-        <v>5.03999999999999</v>
+        <f t="shared" si="0"/>
+        <v>121.96</v>
       </c>
       <c r="H9">
         <f t="shared" si="1"/>
+        <v>5.03999999999999</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="2"/>
         <v>0.0396850393700787</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>-0.09154</v>
-      </c>
-      <c r="J9">
-        <f>($C$3-I9)*10000</f>
-        <v>-34.6</v>
       </c>
       <c r="K9">
         <f t="shared" si="3"/>
+        <v>-34.6</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="4"/>
         <v>0.036421052631579</v>
       </c>
     </row>
-    <row r="10" spans="4:11">
+    <row r="10" spans="4:12">
       <c r="D10" t="s">
         <v>12</v>
       </c>
@@ -3786,77 +3641,77 @@
       <c r="F10">
         <v>0.012288</v>
       </c>
-      <c r="G10">
-        <f>ABS($C$2-F10)*10000</f>
-        <v>4.11999999999999</v>
-      </c>
       <c r="H10">
         <f t="shared" si="1"/>
+        <v>4.11999999999999</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="2"/>
         <v>0.0324409448818897</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>-0.091664</v>
-      </c>
-      <c r="J10">
-        <f>($C$3-I10)*10000</f>
-        <v>-33.3600000000001</v>
       </c>
       <c r="K10">
         <f t="shared" si="3"/>
+        <v>-33.3600000000001</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="4"/>
         <v>0.0351157894736843</v>
       </c>
     </row>
-    <row r="11" spans="5:11">
+    <row r="11" spans="5:12">
       <c r="E11">
         <v>96</v>
       </c>
       <c r="F11">
         <v>0.01227</v>
       </c>
-      <c r="G11">
-        <f>ABS($C$2-F11)*10000</f>
-        <v>4.3</v>
-      </c>
       <c r="H11">
         <f t="shared" si="1"/>
+        <v>4.3</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="2"/>
         <v>0.0338582677165354</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>-0.091616</v>
-      </c>
-      <c r="J11">
-        <f>($C$3-I11)*10000</f>
-        <v>-33.84</v>
       </c>
       <c r="K11">
         <f t="shared" si="3"/>
+        <v>-33.84</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="4"/>
         <v>0.0356210526315789</v>
       </c>
     </row>
-    <row r="12" spans="5:11">
+    <row r="12" spans="5:12">
       <c r="E12">
         <v>120</v>
       </c>
       <c r="F12">
         <v>0.012214</v>
       </c>
-      <c r="G12">
-        <f>ABS($C$2-F12)*10000</f>
-        <v>4.86</v>
-      </c>
       <c r="H12">
         <f t="shared" si="1"/>
+        <v>4.86</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="2"/>
         <v>0.0382677165354331</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>-0.09142</v>
-      </c>
-      <c r="J12">
-        <f>($C$3-I12)*10000</f>
-        <v>-35.8</v>
       </c>
       <c r="K12">
         <f t="shared" si="3"/>
+        <v>-35.8</v>
+      </c>
+      <c r="L12">
+        <f t="shared" si="4"/>
         <v>0.0376842105263158</v>
       </c>
     </row>

--- a/results/meshconv/Rae2822-Gridconv.xlsx
+++ b/results/meshconv/Rae2822-Gridconv.xlsx
@@ -1,15 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\tsagi_dipl\Diploma_bac\results\meshconv\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76779A97-41BB-4DCF-9686-4488638958BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17940"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -21,6 +28,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -74,14 +84,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -89,346 +93,16 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -436,251 +110,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -689,89 +121,158 @@
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -782,7 +283,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -810,163 +311,49 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39994506668294322"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="totalRow" dxfId="14"/>
+      <tableStyleElement type="firstColumn" dxfId="13"/>
+      <tableStyleElement type="lastColumn" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
+      <tableStyleElement type="pageFieldValues" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="zh-CN"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -984,43 +371,55 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr defTabSz="914400">
-              <a:defRPr lang="en-US" sz="1680" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr lang="en-US" sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="75000"/>
                     <a:lumOff val="25000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:ea typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
-                <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:sym typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="ru-RU" altLang="en-US" sz="1680">
-                <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+              <a:rPr lang="ru-RU" altLang="en-US" sz="1600">
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:ea typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
-                <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:sym typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
               </a:rPr>
-              <a:t>Сеточная сходимость на </a:t>
+              <a:t>Сеточная сходимость</a:t>
             </a:r>
             <a:r>
-              <a:rPr altLang="ru-RU" sz="1680">
-                <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+              <a:rPr lang="ru-RU" altLang="en-US" sz="1600" baseline="0">
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:ea typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
-                <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:sym typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+              </a:rPr>
+              <a:t> п</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU" altLang="en-US" sz="1600">
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:sym typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+              </a:rPr>
+              <a:t>ри расчете обтекания </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ru-RU" sz="1600">
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:sym typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
               </a:rPr>
               <a:t>RAE2822 </a:t>
             </a:r>
-            <a:endParaRPr altLang="ru-RU" sz="1680">
-              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
-              <a:ea typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
-              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
-              <a:sym typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
-            </a:endParaRPr>
           </a:p>
         </c:rich>
       </c:tx>
@@ -1029,7 +428,7 @@
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
           <c:x val="0.222270037654653"/>
-          <c:y val="0.0268948655256723"/>
+          <c:y val="2.6894865525672301E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -1040,6 +439,27 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr defTabSz="914400">
+            <a:defRPr lang="en-US" sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:sym typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -1051,15 +471,7 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:strRef>
-              <c:f>"Относительная ошибка Cxa pres"</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Относительная ошибка Cxa pres</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>Относительная ошибка Cxa pres</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="19050" cap="rnd">
@@ -1085,9 +497,6 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:dLbls>
-            <c:delete val="1"/>
-          </c:dLbls>
           <c:xVal>
             <c:numRef>
               <c:f>Sheet1!$E$2:$E$9</c:f>
@@ -1155,6 +564,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-619B-4833-A9CD-C2EC916F983F}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -1202,21 +616,22 @@
                         <a:lumOff val="35000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                     <a:ea typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
-                    <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                     <a:sym typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="ru-RU" altLang="en-US"/>
+                  <a:rPr lang="ru-RU" altLang="en-US">
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:rPr>
                   <a:t>Количество ячеек (тысячи)</a:t>
                 </a:r>
-                <a:endParaRPr lang="ru-RU" altLang="en-US"/>
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -1225,6 +640,27 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr defTabSz="914400">
+                <a:defRPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  <a:sym typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -1255,12 +691,13 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:ea typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
-                <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:sym typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="563040949"/>
@@ -1301,21 +738,50 @@
                         <a:lumOff val="35000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                     <a:ea typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
-                    <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                     <a:sym typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr altLang="ru-RU"/>
-                  <a:t>Cxa (counts)</a:t>
+                  <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                    <a:effectLst/>
+                    <a:sym typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+                  </a:rPr>
+                  <a:t>С</a:t>
                 </a:r>
-                <a:endParaRPr altLang="ru-RU"/>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="-25000">
+                    <a:effectLst/>
+                    <a:sym typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+                  </a:rPr>
+                  <a:t>xa</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ru-RU">
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:rPr>
+                  <a:t> *</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="ru-RU" altLang="ru-RU">
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:rPr>
+                  <a:t> </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ru-RU">
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:rPr>
+                  <a:t>10000</a:t>
+                </a:r>
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -1324,6 +790,27 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr defTabSz="914400">
+                <a:defRPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  <a:sym typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
@@ -1354,12 +841,13 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:ea typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
-                <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:sym typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="561000989"/>
@@ -1416,6 +904,7 @@
           <a:sym typeface="Arial" panose="020B0604020202020204" pitchFamily="7" charset="0"/>
         </a:defRPr>
       </a:pPr>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -1427,9 +916,9 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="zh-CN"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1465,14 +954,12 @@
               <a:t>Ошибка </a:t>
             </a:r>
             <a:r>
-              <a:rPr altLang="ru-RU"/>
+              <a:rPr lang="en-US" altLang="ru-RU"/>
               <a:t>mz</a:t>
             </a:r>
-            <a:endParaRPr altLang="ru-RU"/>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1481,6 +968,27 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr defTabSz="914400">
+            <a:defRPr lang="en-US" sz="1680" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
+              <a:ea typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
+              <a:sym typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -1492,15 +1000,7 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:strRef>
-              <c:f>"Относительная ошибка mz pres"</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Относительная ошибка mz pres</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>Относительная ошибка mz pres</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="19050" cap="rnd">
@@ -1526,9 +1026,6 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:dLbls>
-            <c:delete val="1"/>
-          </c:dLbls>
           <c:xVal>
             <c:numRef>
               <c:f>Sheet1!$E$2:$E$9</c:f>
@@ -1569,33 +1066,38 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>-0.096364</c:v>
+                  <c:v>-9.6364000000000005E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-0.093317</c:v>
+                  <c:v>-9.3316999999999997E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-0.092746</c:v>
+                  <c:v>-9.2745999999999995E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-0.09218</c:v>
+                  <c:v>-9.2179999999999998E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-0.091965</c:v>
+                  <c:v>-9.1965000000000005E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-0.0914</c:v>
+                  <c:v>-9.1399999999999995E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-0.091965</c:v>
+                  <c:v>-9.1965000000000005E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-0.09154</c:v>
+                  <c:v>-9.1539999999999996E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8521-460A-A9E6-C147465468B3}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -1663,6 +1165,7 @@
                 <a:sym typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="563040949"/>
@@ -1724,6 +1227,7 @@
                 <a:sym typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="561000989"/>
@@ -1766,10 +1270,10 @@
                 <a:sym typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
       </c:legendEntry>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1796,6 +1300,7 @@
               <a:sym typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -1835,11 +1340,14 @@
           <a:sym typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
         </a:defRPr>
       </a:pPr>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
-  <c:externalData r:id="rId1">
-    <c:autoUpdate val="0"/>
-  </c:externalData>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
@@ -3000,28 +2508,34 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>53975</xdr:colOff>
+      <xdr:colOff>53974</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>29845</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
-      <xdr:colOff>84455</xdr:colOff>
+      <xdr:colOff>209549</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>144145</xdr:rowOff>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="13179425" y="791845"/>
-        <a:ext cx="6126480" cy="4114800"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3044,14 +2558,20 @@
       <xdr:row>52</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 3"/>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="8972550" y="6143625"/>
-        <a:ext cx="5902325" cy="3895725"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3316,21 +2836,21 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L17"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="5" max="5" width="22.7142857142857" customWidth="1"/>
-    <col min="6" max="6" width="9.57142857142857"/>
-    <col min="7" max="8" width="25.8571428571429" customWidth="1"/>
-    <col min="9" max="9" width="20.2857142857143" customWidth="1"/>
-    <col min="11" max="11" width="20.2857142857143" customWidth="1"/>
-    <col min="12" max="12" width="17.4285714285714" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
+    <col min="6" max="6" width="9.5703125"/>
+    <col min="7" max="8" width="25.85546875" customWidth="1"/>
+    <col min="9" max="9" width="20.28515625" customWidth="1"/>
+    <col min="11" max="11" width="20.28515625" customWidth="1"/>
+    <col min="12" max="12" width="17.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -3341,7 +2861,7 @@
         <v>1</v>
       </c>
       <c r="C1">
-        <v>0.743</v>
+        <v>0.74299999999999999</v>
       </c>
       <c r="E1" t="s">
         <v>2</v>
@@ -3373,7 +2893,7 @@
         <v>3</v>
       </c>
       <c r="C2">
-        <v>0.0127</v>
+        <v>1.2699999999999999E-2</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -3382,7 +2902,7 @@
         <v>16</v>
       </c>
       <c r="F2">
-        <v>0.013468</v>
+        <v>1.3468000000000001E-2</v>
       </c>
       <c r="G2">
         <f>F2*10000</f>
@@ -3390,14 +2910,14 @@
       </c>
       <c r="H2">
         <f>($C$2-F2)*10000</f>
-        <v>-7.68000000000001</v>
+        <v>-7.6800000000000104</v>
       </c>
       <c r="I2">
         <f>($C$2-F2)/$C$2</f>
-        <v>-0.060472440944882</v>
+        <v>-6.0472440944882001E-2</v>
       </c>
       <c r="J2">
-        <v>-0.096364</v>
+        <v>-9.6364000000000005E-2</v>
       </c>
       <c r="K2">
         <f>($C$3-J2)*10000</f>
@@ -3405,21 +2925,21 @@
       </c>
       <c r="L2">
         <f>(C$3-J2)/$C$3</f>
-        <v>-0.0143578947368421</v>
+        <v>-1.4357894736842101E-2</v>
       </c>
     </row>
-    <row r="3" spans="2:12">
+    <row r="3" spans="1:12">
       <c r="B3" t="s">
         <v>11</v>
       </c>
       <c r="C3">
-        <v>-0.095</v>
+        <v>-9.5000000000000001E-2</v>
       </c>
       <c r="E3">
         <v>33</v>
       </c>
       <c r="F3">
-        <v>0.012255</v>
+        <v>1.2255E-2</v>
       </c>
       <c r="G3">
         <f t="shared" ref="G3:G9" si="0">F3*10000</f>
@@ -3427,30 +2947,30 @@
       </c>
       <c r="H3">
         <f t="shared" ref="H3:H12" si="1">ABS($C$2-F3)*10000</f>
-        <v>4.44999999999999</v>
+        <v>4.4499999999999904</v>
       </c>
       <c r="I3">
         <f t="shared" ref="I3:I12" si="2">($C$2-F3)/$C$2</f>
-        <v>0.0350393700787401</v>
+        <v>3.5039370078740098E-2</v>
       </c>
       <c r="J3">
-        <v>-0.093317</v>
+        <v>-9.3316999999999997E-2</v>
       </c>
       <c r="K3">
         <f t="shared" ref="K3:K12" si="3">($C$3-J3)*10000</f>
-        <v>-16.83</v>
+        <v>-16.829999999999998</v>
       </c>
       <c r="L3">
         <f t="shared" ref="L3:L12" si="4">(C$3-J3)/$C$3</f>
-        <v>0.0177157894736843</v>
+        <v>1.7715789473684299E-2</v>
       </c>
     </row>
-    <row r="4" spans="5:12">
+    <row r="4" spans="1:12">
       <c r="E4">
         <v>53</v>
       </c>
       <c r="F4">
-        <v>0.012113</v>
+        <v>1.2113000000000001E-2</v>
       </c>
       <c r="G4">
         <f t="shared" si="0"/>
@@ -3458,30 +2978,30 @@
       </c>
       <c r="H4">
         <f t="shared" si="1"/>
-        <v>5.86999999999999</v>
+        <v>5.8699999999999903</v>
       </c>
       <c r="I4">
         <f t="shared" si="2"/>
-        <v>0.0462204724409448</v>
+        <v>4.62204724409448E-2</v>
       </c>
       <c r="J4">
-        <v>-0.092746</v>
+        <v>-9.2745999999999995E-2</v>
       </c>
       <c r="K4">
         <f t="shared" si="3"/>
-        <v>-22.5400000000001</v>
+        <v>-22.540000000000099</v>
       </c>
       <c r="L4">
         <f t="shared" si="4"/>
-        <v>0.0237263157894737</v>
+        <v>2.37263157894737E-2</v>
       </c>
     </row>
-    <row r="5" spans="5:12">
+    <row r="5" spans="1:12">
       <c r="E5">
         <v>78</v>
       </c>
       <c r="F5">
-        <v>0.012188</v>
+        <v>1.2187999999999999E-2</v>
       </c>
       <c r="G5">
         <f t="shared" si="0"/>
@@ -3493,10 +3013,10 @@
       </c>
       <c r="I5">
         <f t="shared" si="2"/>
-        <v>0.0403149606299213</v>
+        <v>4.03149606299213E-2</v>
       </c>
       <c r="J5">
-        <v>-0.09218</v>
+        <v>-9.2179999999999998E-2</v>
       </c>
       <c r="K5">
         <f t="shared" si="3"/>
@@ -3504,15 +3024,15 @@
       </c>
       <c r="L5">
         <f t="shared" si="4"/>
-        <v>0.0296842105263158</v>
+        <v>2.9684210526315799E-2</v>
       </c>
     </row>
-    <row r="6" spans="5:12">
+    <row r="6" spans="1:12">
       <c r="E6">
         <v>96</v>
       </c>
       <c r="F6">
-        <v>0.012182</v>
+        <v>1.2182E-2</v>
       </c>
       <c r="G6">
         <f t="shared" si="0"/>
@@ -3520,14 +3040,14 @@
       </c>
       <c r="H6">
         <f t="shared" si="1"/>
-        <v>5.17999999999999</v>
+        <v>5.1799999999999899</v>
       </c>
       <c r="I6">
         <f t="shared" si="2"/>
-        <v>0.0407874015748031</v>
+        <v>4.0787401574803102E-2</v>
       </c>
       <c r="J6">
-        <v>-0.091965</v>
+        <v>-9.1965000000000005E-2</v>
       </c>
       <c r="K6">
         <f t="shared" si="3"/>
@@ -3535,15 +3055,15 @@
       </c>
       <c r="L6">
         <f t="shared" si="4"/>
-        <v>0.0319473684210526</v>
+        <v>3.1947368421052599E-2</v>
       </c>
     </row>
-    <row r="7" spans="5:12">
+    <row r="7" spans="1:12">
       <c r="E7">
         <v>121</v>
       </c>
       <c r="F7">
-        <v>0.012184</v>
+        <v>1.2184E-2</v>
       </c>
       <c r="G7">
         <f t="shared" si="0"/>
@@ -3551,30 +3071,30 @@
       </c>
       <c r="H7">
         <f t="shared" si="1"/>
-        <v>5.15999999999999</v>
+        <v>5.1599999999999904</v>
       </c>
       <c r="I7">
         <f t="shared" si="2"/>
-        <v>0.0406299212598425</v>
+        <v>4.0629921259842501E-2</v>
       </c>
       <c r="J7">
-        <v>-0.0914</v>
+        <v>-9.1399999999999995E-2</v>
       </c>
       <c r="K7">
         <f t="shared" si="3"/>
-        <v>-36.0000000000001</v>
+        <v>-36.000000000000099</v>
       </c>
       <c r="L7">
         <f t="shared" si="4"/>
-        <v>0.0378947368421053</v>
+        <v>3.78947368421053E-2</v>
       </c>
     </row>
-    <row r="8" spans="5:12">
+    <row r="8" spans="1:12">
       <c r="E8">
         <v>145</v>
       </c>
       <c r="F8">
-        <v>0.012182</v>
+        <v>1.2182E-2</v>
       </c>
       <c r="G8">
         <f t="shared" si="0"/>
@@ -3582,14 +3102,14 @@
       </c>
       <c r="H8">
         <f t="shared" si="1"/>
-        <v>5.17999999999999</v>
+        <v>5.1799999999999899</v>
       </c>
       <c r="I8">
         <f t="shared" si="2"/>
-        <v>0.0407874015748031</v>
+        <v>4.0787401574803102E-2</v>
       </c>
       <c r="J8">
-        <v>-0.091965</v>
+        <v>-9.1965000000000005E-2</v>
       </c>
       <c r="K8">
         <f t="shared" si="3"/>
@@ -3597,15 +3117,15 @@
       </c>
       <c r="L8">
         <f t="shared" si="4"/>
-        <v>0.0319473684210526</v>
+        <v>3.1947368421052599E-2</v>
       </c>
     </row>
-    <row r="9" spans="5:12">
+    <row r="9" spans="1:12">
       <c r="E9">
         <v>200</v>
       </c>
       <c r="F9">
-        <v>0.012196</v>
+        <v>1.2196E-2</v>
       </c>
       <c r="G9">
         <f t="shared" si="0"/>
@@ -3613,14 +3133,14 @@
       </c>
       <c r="H9">
         <f t="shared" si="1"/>
-        <v>5.03999999999999</v>
+        <v>5.0399999999999903</v>
       </c>
       <c r="I9">
         <f t="shared" si="2"/>
-        <v>0.0396850393700787</v>
+        <v>3.9685039370078702E-2</v>
       </c>
       <c r="J9">
-        <v>-0.09154</v>
+        <v>-9.1539999999999996E-2</v>
       </c>
       <c r="K9">
         <f t="shared" si="3"/>
@@ -3628,10 +3148,10 @@
       </c>
       <c r="L9">
         <f t="shared" si="4"/>
-        <v>0.036421052631579</v>
+        <v>3.6421052631579E-2</v>
       </c>
     </row>
-    <row r="10" spans="4:12">
+    <row r="10" spans="1:12">
       <c r="D10" t="s">
         <v>12</v>
       </c>
@@ -3639,34 +3159,34 @@
         <v>78</v>
       </c>
       <c r="F10">
-        <v>0.012288</v>
+        <v>1.2288E-2</v>
       </c>
       <c r="H10">
         <f t="shared" si="1"/>
-        <v>4.11999999999999</v>
+        <v>4.1199999999999903</v>
       </c>
       <c r="I10">
         <f t="shared" si="2"/>
-        <v>0.0324409448818897</v>
+        <v>3.2440944881889699E-2</v>
       </c>
       <c r="J10">
-        <v>-0.091664</v>
+        <v>-9.1663999999999995E-2</v>
       </c>
       <c r="K10">
         <f t="shared" si="3"/>
-        <v>-33.3600000000001</v>
+        <v>-33.360000000000099</v>
       </c>
       <c r="L10">
         <f t="shared" si="4"/>
-        <v>0.0351157894736843</v>
+        <v>3.5115789473684302E-2</v>
       </c>
     </row>
-    <row r="11" spans="5:12">
+    <row r="11" spans="1:12">
       <c r="E11">
         <v>96</v>
       </c>
       <c r="F11">
-        <v>0.01227</v>
+        <v>1.227E-2</v>
       </c>
       <c r="H11">
         <f t="shared" si="1"/>
@@ -3674,45 +3194,45 @@
       </c>
       <c r="I11">
         <f t="shared" si="2"/>
-        <v>0.0338582677165354</v>
+        <v>3.3858267716535398E-2</v>
       </c>
       <c r="J11">
-        <v>-0.091616</v>
+        <v>-9.1616000000000003E-2</v>
       </c>
       <c r="K11">
         <f t="shared" si="3"/>
-        <v>-33.84</v>
+        <v>-33.840000000000003</v>
       </c>
       <c r="L11">
         <f t="shared" si="4"/>
-        <v>0.0356210526315789</v>
+        <v>3.5621052631578901E-2</v>
       </c>
     </row>
-    <row r="12" spans="5:12">
+    <row r="12" spans="1:12">
       <c r="E12">
         <v>120</v>
       </c>
       <c r="F12">
-        <v>0.012214</v>
+        <v>1.2213999999999999E-2</v>
       </c>
       <c r="H12">
         <f t="shared" si="1"/>
-        <v>4.86</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="I12">
         <f t="shared" si="2"/>
-        <v>0.0382677165354331</v>
+        <v>3.8267716535433101E-2</v>
       </c>
       <c r="J12">
-        <v>-0.09142</v>
+        <v>-9.1420000000000001E-2</v>
       </c>
       <c r="K12">
         <f t="shared" si="3"/>
-        <v>-35.8</v>
+        <v>-35.799999999999997</v>
       </c>
       <c r="L12">
         <f t="shared" si="4"/>
-        <v>0.0376842105263158</v>
+        <v>3.7684210526315799E-2</v>
       </c>
     </row>
     <row r="17" spans="1:1">
@@ -3722,7 +3242,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>